--- a/stories/arbres/ATOM-FAM.VER.001-04.xlsx
+++ b/stories/arbres/ATOM-FAM.VER.001-04.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Aïcha est dans sa chambre. Un petit pot de terre est sur la table. Aïcha veut le déplacer. Le pot glisse. La terre tombe. Ça fait un tas brun. Le tapis est sale. Aïcha a le ventre serré. Elle va vers papa. Aïcha dit : papa, le pot a glissé. J'ai fait tomber la terre. Papa s'approche. Papa dit : merci de raconter. On ramasse ensemble. Aïcha prend la petite pelle. Papa tient le seau. La terre revient dans le pot. Maman entre. Aïcha dit : maman, j'ai raconté. Le pot est tombé. Maman écoute. Maman dit : merci Aïcha. On raconte à papa ou maman. Parce qu'elle a raconté, papa et maman peuvent aider. Parce que papa et maman savent, le tapis redevient propre. Aïcha souffle.</t>
+          <t>Aïcha est dans sa chambre. Un petit pot de terre est sur la table. Aïcha veut le déplacer. Le pot glisse. La terre tombe. Ça fait un tas brun. Le tapis est sale. Aïcha a le ventre serré. Elle va vers papa. Papa, le pot a glissé. J'ai fait tomber la terre. Papa s'approche. Merci de raconter. On ramasse ensemble. Aïcha prend la petite pelle. Papa tient le seau. La terre revient dans le pot. Maman entre. Maman, j'ai raconté. Le pot est tombé. Maman écoute. Merci Aïcha. On raconte à papa ou maman. Parce qu'elle a raconté, papa et maman peuvent aider. Parce que papa et maman savent, le tapis redevient propre. Aïcha souffle.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,18 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Aïcha est dans sa chambre. Un petit pot de terre est sur la table. Aïcha veut le déplacer. Le pot glisse. La terre tombe. Ça fait un tas brun. Le tapis est sale. Aïcha a le ventre serré. Elle va vers papa.
+enfant-f|Papa, le pot a glissé. J'ai fait tomber la terre. Papa s'approche.
+papa|Merci de raconter. On ramasse ensemble.
+narrateur|Aïcha prend la petite pelle. Papa tient le seau. La terre revient dans le pot. Maman entre.
+enfant-f|Maman, j'ai raconté.
+narrateur|Le pot est tombé. Maman écoute.
+maman|Merci Aïcha. On raconte à papa ou maman. Parce qu'elle a raconté, papa et maman peuvent aider. Parce que papa et maman savent, le tapis redevient propre.
+narrateur|Aïcha souffle.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1493,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|La terre est tombée. Que fait Aïcha ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1666,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Aïcha a raconté. Papa et maman ont écouté. Raconter, c'est bien.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1829,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Aïcha pose le pot. Le tapis est propre.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1996,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2019,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2036,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-FAM.VER.001-04.xlsx
+++ b/stories/arbres/ATOM-FAM.VER.001-04.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1317,6 +1322,11 @@
 narrateur|Aïcha souffle.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1500,6 +1510,7 @@
           <t>narrateur|La terre est tombée. Que fait Aïcha ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1671,6 +1682,7 @@
           <t>narrateur|Aïcha a raconté. Papa et maman ont écouté. Raconter, c'est bien.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1834,6 +1846,7 @@
           <t>narrateur|Aïcha pose le pot. Le tapis est propre.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2001,6 +2014,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2019,7 +2033,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2043,6 +2057,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2057,7 +2085,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2244,6 +2272,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-FAM.VER.001-04.xlsx
+++ b/stories/arbres/ATOM-FAM.VER.001-04.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Aïcha raconte le pot de terre</t>
+          <t>Nino raconte le pot de terre</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Nino veut déplacer un petit pot. La terre tombe sur le tapis. Il raconte à papa, puis à maman. Ils ramassent ensemble.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Aïcha est dans sa chambre. Un petit pot de terre est sur la table. Aïcha veut le déplacer. Le pot glisse. La terre tombe. Ça fait un tas brun. Le tapis est sale. Aïcha a le ventre serré. Elle va vers papa. Papa, le pot a glissé. J'ai fait tomber la terre. Papa s'approche. Merci de raconter. On ramasse ensemble. Aïcha prend la petite pelle. Papa tient le seau. La terre revient dans le pot. Maman entre. Maman, j'ai raconté. Le pot est tombé. Maman écoute. Merci Aïcha. On raconte à papa ou maman. Parce qu'elle a raconté, papa et maman peuvent aider. Parce que papa et maman savent, le tapis redevient propre. Aïcha souffle.</t>
+          <t>Une veilleuse brille encore un peu. Elle fait un rond orange au mur. Un cheval de bois attend près du lit. Sa crinière est lisse. Un rayon de lumière traverse la chambre. De la poussière danse dedans. Le tapis est épais et doux. La fenêtre est un peu ouverte. Un oiseau chante, loin. Une chaussette traîne sous le lit. Un petit pot de terre est sur la table. Tu as vu la poussière, Nino ? Oui, papa. Elle danse. Le cheval de bois attend. Tu lui as dit bonjour ? Oui. Tout bas. En ce moment, Nino approche le petit pot. Il veut déplacer le petit pot. Le pot glisse. La terre tombe. Ça fait un tas brun. Le tapis est sale. Nino a le ventre serré. Il va vers papa. Papa, le pot a glissé. J'ai fait tomber la terre. Je t'écoute, Nino. Merci de raconter. On ramasse ensemble. Tu as fait du bon travail. Tu veux la petite pelle ? Oui, papa. Nino prend la petite pelle. Papa tient le seau. La terre revient dans le pot. Ça fait un bruit de grains. Maman entre. Elle apporte une chaussette pliée. Maman, j'ai raconté. Le pot est tombé. Je t'écoute. Merci Nino. On raconte à papa ou maman. Bravo. Parce que tu as raconté, on peut aider. Le tapis redevient propre. Nino souffle. Tu veux poser le pot plus loin ? Oui. Sur la table, au milieu. On brosse encore un peu le tapis ? Oui. Tout doux. Le tapis redevient beige. Le cheval de bois a vu, lui aussi. Il a vu. Je lui ai raconté tout bas. Tu as raconté à papa. Puis à maman. C'est le bon geste.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,19 +1324,73 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Aïcha est dans sa chambre. Un petit pot de terre est sur la table. Aïcha veut le déplacer. Le pot glisse. La terre tombe. Ça fait un tas brun. Le tapis est sale. Aïcha a le ventre serré. Elle va vers papa.
-enfant-f|Papa, le pot a glissé. J'ai fait tomber la terre. Papa s'approche.
-papa|Merci de raconter. On ramasse ensemble.
-narrateur|Aïcha prend la petite pelle. Papa tient le seau. La terre revient dans le pot. Maman entre.
-enfant-f|Maman, j'ai raconté.
-narrateur|Le pot est tombé. Maman écoute.
-maman|Merci Aïcha. On raconte à papa ou maman. Parce qu'elle a raconté, papa et maman peuvent aider. Parce que papa et maman savent, le tapis redevient propre.
-narrateur|Aïcha souffle.</t>
+          <t>narrateur|Une veilleuse brille encore un peu.
+narrateur|Elle fait un rond orange au mur.
+narrateur|Un cheval de bois attend près du lit.
+narrateur|Sa crinière est lisse.
+narrateur|Un rayon de lumière traverse la chambre.
+narrateur|De la poussière danse dedans.
+narrateur|Le tapis est épais et doux.
+narrateur|La fenêtre est un peu ouverte.
+narrateur|Un oiseau chante, loin.
+narrateur|Une chaussette traîne sous le lit.
+narrateur|Un petit pot de terre est sur la table.
+papa|Tu as vu la poussière, Nino ?
+enfant-m|Oui, papa.
+enfant-m|Elle danse.
+papa|Le cheval de bois attend.
+papa|Tu lui as dit bonjour ?
+enfant-m|Oui.
+enfant-m|Tout bas.
+narrateur|En ce moment, Nino approche le petit pot.
+narrateur|Il veut déplacer le petit pot.
+narrateur|Le pot glisse.
+narrateur|La terre tombe.
+narrateur|Ça fait un tas brun.
+narrateur|Le tapis est sale.
+narrateur|Nino a le ventre serré.
+narrateur|Il va vers papa.
+enfant-m|Papa, le pot a glissé.
+enfant-m|J'ai fait tomber la terre.
+papa|Je t'écoute, Nino.
+papa|Merci de raconter.
+papa|On ramasse ensemble.
+papa|Tu as fait du bon travail.
+papa|Tu veux la petite pelle ?
+enfant-m|Oui, papa.
+narrateur|Nino prend la petite pelle.
+narrateur|Papa tient le seau.
+narrateur|La terre revient dans le pot.
+narrateur|Ça fait un bruit de grains.
+narrateur|Maman entre.
+narrateur|Elle apporte une chaussette pliée.
+enfant-m|Maman, j'ai raconté.
+enfant-m|Le pot est tombé.
+maman|Je t'écoute.
+maman|Merci Nino.
+maman|On raconte à papa ou maman.
+maman|Bravo.
+maman|Parce que tu as raconté, on peut aider.
+maman|Le tapis redevient propre.
+narrateur|Nino souffle.
+papa|Tu veux poser le pot plus loin ?
+enfant-m|Oui.
+enfant-m|Sur la table, au milieu.
+maman|On brosse encore un peu le tapis ?
+enfant-m|Oui.
+enfant-m|Tout doux.
+narrateur|Le tapis redevient beige.
+papa|Le cheval de bois a vu, lui aussi.
+enfant-m|Il a vu.
+enfant-m|Je lui ai raconté tout bas.
+maman|Tu as raconté à papa.
+maman|Puis à maman.
+maman|C'est le bon geste.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>enfants_parc</t>
+          <t>veilleuse,terre_pot</t>
         </is>
       </c>
     </row>
@@ -1351,7 +1417,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>La terre est tombée. Que fait Aïcha ?</t>
+          <t>La terre est tombée. Que fait Nino ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1507,7 +1573,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|La terre est tombée. Que fait Aïcha ?</t>
+          <t>narrateur|La terre est tombée.
+narrateur|Que fait Nino ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1535,7 +1602,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Aïcha a raconté. Papa et maman ont écouté. Raconter, c'est bien.</t>
+          <t>Nino a raconté. Papa et maman ont écouté. Merci d'avoir raconté. On raconte à papa ou maman. Bravo, Nino. J'ai raconté. On a ramassé. Oui. C'est du bon travail.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1679,7 +1746,15 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Aïcha a raconté. Papa et maman ont écouté. Raconter, c'est bien.</t>
+          <t>narrateur|Nino a raconté.
+narrateur|Papa et maman ont écouté.
+papa|Merci d'avoir raconté.
+maman|On raconte à papa ou maman.
+papa|Bravo, Nino.
+enfant-m|J'ai raconté.
+enfant-m|On a ramassé.
+maman|Oui.
+maman|C'est du bon travail.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1707,7 +1782,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Aïcha pose le pot. Le tapis est propre.</t>
+          <t>Nino pose le pot. Le tapis est propre. Tu veux éteindre la veilleuse ? Oui. Le rond orange part. Le cheval de bois est encore là. Il attend. Le rayon de lumière est plus court. L'oiseau chante encore, plus loin. On reste un peu sur le tapis ? Oui. Il est doux. Tu ramasses la chaussette, avec moi ? Oui. Celle sous le lit.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1843,7 +1918,21 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Aïcha pose le pot. Le tapis est propre.</t>
+          <t>narrateur|Nino pose le pot.
+narrateur|Le tapis est propre.
+maman|Tu veux éteindre la veilleuse ?
+enfant-m|Oui.
+enfant-m|Le rond orange part.
+papa|Le cheval de bois est encore là.
+enfant-m|Il attend.
+narrateur|Le rayon de lumière est plus court.
+narrateur|L'oiseau chante encore, plus loin.
+maman|On reste un peu sur le tapis ?
+enfant-m|Oui.
+enfant-m|Il est doux.
+papa|Tu ramasses la chaussette, avec moi ?
+enfant-m|Oui.
+enfant-m|Celle sous le lit.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1871,7 +1960,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai raconté. Papa a écouté. Bravo. Tu as fait du bon travail. Le petit pot tient bien, au milieu. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2011,7 +2100,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai raconté.
+enfant-m|Papa a écouté.
+papa|Bravo.
+maman|Tu as fait du bon travail.
+narrateur|Le petit pot tient bien, au milieu.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2033,7 +2127,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2071,6 +2165,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-FAM.VER.001-04.xlsx
+++ b/stories/arbres/ATOM-FAM.VER.001-04.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Une veilleuse brille encore un peu. Elle fait un rond orange au mur. Un cheval de bois attend près du lit. Sa crinière est lisse. Un rayon de lumière traverse la chambre. De la poussière danse dedans. Le tapis est épais et doux. La fenêtre est un peu ouverte. Un oiseau chante, loin. Une chaussette traîne sous le lit. Un petit pot de terre est sur la table. Tu as vu la poussière, Nino ? Oui, papa. Elle danse. Le cheval de bois attend. Tu lui as dit bonjour ? Oui. Tout bas. En ce moment, Nino approche le petit pot. Il veut déplacer le petit pot. Le pot glisse. La terre tombe. Ça fait un tas brun. Le tapis est sale. Nino a le ventre serré. Il va vers papa. Papa, le pot a glissé. J'ai fait tomber la terre. Je t'écoute, Nino. Merci de raconter. On ramasse ensemble. Tu as fait du bon travail. Tu veux la petite pelle ? Oui, papa. Nino prend la petite pelle. Papa tient le seau. La terre revient dans le pot. Ça fait un bruit de grains. Maman entre. Elle apporte une chaussette pliée. Maman, j'ai raconté. Le pot est tombé. Je t'écoute. Merci Nino. On raconte à papa ou maman. Bravo. Parce que tu as raconté, on peut aider. Le tapis redevient propre. Nino souffle. Tu veux poser le pot plus loin ? Oui. Sur la table, au milieu. On brosse encore un peu le tapis ? Oui. Tout doux. Le tapis redevient beige. Le cheval de bois a vu, lui aussi. Il a vu. Je lui ai raconté tout bas. Tu as raconté à papa. Puis à maman. C'est le bon geste.</t>
+          <t>Une veilleuse brille encore un peu. Elle fait un rond orange au mur. Un cheval de bois attend près du lit. Sa crinière est lisse. Un rayon de lumière traverse la chambre. De la poussière danse dedans. Le tapis est épais et doux. La fenêtre est un peu ouverte. Un oiseau chante, loin. Une chaussette traîne sous le lit. Un petit pot de terre est sur la table. Tu as vu la poussière, Nino ? Oui, papa. Elle danse. Le cheval de bois attend. Tu lui as dit bonjour ? Oui. Tout bas. En ce moment, Nino approche le petit pot. Il veut déplacer le petit pot. Le pot glisse. La terre tombe. Ça fait un tas brun. Le tapis est sale. Nino a le ventre serré. Il va vers papa. Papa, le pot a glissé. J'ai fait tomber la terre. Je t'écoute, Nino. Merci de raconter. On ramasse ensemble. Tu veux la petite pelle ? Oui, papa. Nino prend la petite pelle. Papa tient le seau. La terre revient dans le pot. Ça fait un bruit de grains. Maman entre. Elle apporte une chaussette pliée. Maman, j'ai raconté. Le pot est tombé. Je t'écoute. Merci Nino. On raconte à papa ou maman. Bravo. Parce que tu as raconté, on peut aider. Le tapis redevient propre. Nino souffle. Tu veux poser le pot plus loin ? Oui. Sur la table, au milieu. On brosse encore un peu le tapis ? Oui. Tout doux. Le tapis redevient beige. Le cheval de bois a vu, lui aussi. Il a vu. Je lui ai raconté tout bas. Tu as raconté à papa. Puis à maman. C'est le bon geste.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Aïcha est dans sa chambre. Un petit pot de terre est sur la table. Aïcha veut le déplacer. Le pot glisse. La terre tombe. Ça fait un tas brun. Le tapis est sale. Aïcha a le ventre serré. Elle va vers papa. Aïcha dit : papa, le pot a glissé. J'ai fait tomber la terre. Papa s'approche. Papa dit : merci de &lt;emphasis level="moderate"&gt;raconter&lt;/emphasis&gt;. On ramasse ensemble. Aïcha prend la petite pelle. Papa tient le seau. La terre revient dans le pot. Maman entre. Aïcha dit : maman, j'ai raconté. Le pot est tombé. Maman écoute. Maman dit : merci Aïcha. On raconte à papa ou maman. Parce qu'elle a raconté, papa et maman peuvent aider. Parce que papa et maman savent, le tapis redevient propre. Aïcha souffle.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Une veilleuse brille encore un peu. Elle fait un rond orange au mur. Un cheval de bois attend près du lit. Sa crinière est lisse. Un rayon de lumière traverse la chambre. De la poussière danse dedans. Le tapis est épais et doux. La fenêtre est un peu ouverte. Un oiseau chante, loin. Une chaussette traîne sous le lit. Un petit pot de terre est sur la table. Tu as vu la poussière, Nino ? Oui, papa. Elle danse. Le cheval de bois attend. Tu lui as dit bonjour ? Oui. Tout bas. En ce moment, Nino approche le petit pot. Il veut déplacer le petit pot. Le pot glisse. La terre tombe. Ça fait un tas brun. Le tapis est sale. Nino a le ventre serré. Il va vers papa. Papa, le pot a glissé. J'ai fait tomber la terre. Je t'écoute, Nino. Merci de raconter. On ramasse ensemble. Tu veux la petite pelle ? Oui, papa. Nino prend la petite pelle. Papa tient le seau. La terre revient dans le pot. Ça fait un bruit de grains. Maman entre. Elle apporte une chaussette pliée. Maman, j'ai raconté. Le pot est tombé. Je t'écoute. Merci Nino. On raconte à papa ou maman. Bravo. Parce que tu as raconté, on peut aider. Le tapis redevient propre. Nino souffle. Tu veux poser le pot plus loin ? Oui. Sur la table, au milieu. On brosse encore un peu le tapis ? Oui. Tout doux. Le tapis redevient beige. Le cheval de bois a vu, lui aussi. Il a vu. Je lui ai raconté tout bas. Tu as raconté à papa. Puis à maman. C'est le bon geste.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1355,7 +1355,6 @@
 papa|Je t'écoute, Nino.
 papa|Merci de raconter.
 papa|On ramasse ensemble.
-papa|Tu as fait du bon travail.
 papa|Tu veux la petite pelle ?
 enfant-m|Oui, papa.
 narrateur|Nino prend la petite pelle.
@@ -1422,7 +1421,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;La terre est tombée. Que fait Aïcha ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>La terre est tombée. Que fait Nino ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1577,7 +1576,6 @@
 narrateur|Que fait Nino ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1602,12 +1600,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Nino a raconté. Papa et maman ont écouté. Merci d'avoir raconté. On raconte à papa ou maman. Bravo, Nino. J'ai raconté. On a ramassé. Oui. C'est du bon travail.</t>
+          <t>Nino a raconté. Papa et maman ont écouté. Merci d'avoir raconté. On raconte à papa ou maman. Bravo, Nino. J'ai raconté. On a ramassé. Oui.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Aïcha a raconté. Papa et maman ont écouté. &lt;emphasis level="moderate"&gt;raconter&lt;/emphasis&gt;, c'est bien.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nino a raconté. Papa et maman ont écouté. Merci d'avoir raconté. On raconte à papa ou maman. Bravo, Nino. J'ai raconté. On a ramassé. Oui.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1753,11 +1751,9 @@
 papa|Bravo, Nino.
 enfant-m|J'ai raconté.
 enfant-m|On a ramassé.
-maman|Oui.
-maman|C'est du bon travail.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+maman|Oui.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1787,7 +1783,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Aïcha pose le pot. Le tapis est propre.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nino pose le pot. Le tapis est propre. Tu veux éteindre la veilleuse ? Oui. Le rond orange part. Le cheval de bois est encore là. Il attend. Le rayon de lumière est plus court. L'oiseau chante encore, plus loin. On reste un peu sur le tapis ? Oui. Il est doux. Tu ramasses la chaussette, avec moi ? Oui. Celle sous le lit.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1935,7 +1931,6 @@
 enfant-m|Celle sous le lit.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1960,12 +1955,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai raconté. Papa a écouté. Bravo. Tu as fait du bon travail. Le petit pot tient bien, au milieu. L'histoire est finie.</t>
+          <t>J'ai raconté. Papa a écouté. Bravo. Le petit pot tient bien, au milieu.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'ai raconté. Papa a écouté. Bravo. Le petit pot tient bien, au milieu.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2103,12 +2098,9 @@
           <t>enfant-m|J'ai raconté.
 enfant-m|Papa a écouté.
 papa|Bravo.
-maman|Tu as fait du bon travail.
-narrateur|Le petit pot tient bien, au milieu.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|Le petit pot tient bien, au milieu.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2127,7 +2119,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2172,6 +2164,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-FAM.VER.001-04.xlsx
+++ b/stories/arbres/ATOM-FAM.VER.001-04.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Aïcha, papa, maman</t>
+          <t>Nino, papa, maman</t>
         </is>
       </c>
     </row>
